--- a/artfynd/A 25708-2026 artfynd.xlsx
+++ b/artfynd/A 25708-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908819</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908835</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908834</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908815</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908814</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908808</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1653,6 +1703,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908838</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908810</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908811</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908826</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908807</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908831</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908832</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908828</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908829</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908830</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908840</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2758,8 +2863,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134908837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25708-2026 artfynd.xlsx
+++ b/artfynd/A 25708-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134908817</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134908819</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>134908813</v>
       </c>
       <c r="B4" t="n">
-        <v>96106</v>
+        <v>96150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>134908835</v>
       </c>
       <c r="B5" t="n">
-        <v>97889</v>
+        <v>97933</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>134908834</v>
       </c>
       <c r="B6" t="n">
-        <v>97873</v>
+        <v>97917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>134908815</v>
       </c>
       <c r="B7" t="n">
-        <v>96512</v>
+        <v>96556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>134908814</v>
       </c>
       <c r="B8" t="n">
-        <v>96501</v>
+        <v>96545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>134908808</v>
       </c>
       <c r="B9" t="n">
-        <v>96423</v>
+        <v>96467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>134908839</v>
       </c>
       <c r="B10" t="n">
-        <v>96423</v>
+        <v>96467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>134908838</v>
       </c>
       <c r="B11" t="n">
-        <v>96533</v>
+        <v>96577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>134908810</v>
       </c>
       <c r="B12" t="n">
-        <v>83341</v>
+        <v>83381</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>134908826</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>134908831</v>
       </c>
       <c r="B16" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>134908832</v>
       </c>
       <c r="B17" t="n">
-        <v>110159</v>
+        <v>110215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>134908828</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134908829</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>134908830</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>134908840</v>
       </c>
       <c r="B21" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>134908837</v>
       </c>
       <c r="B22" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
